--- a/data/trans_bre/P16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 6,25</t>
+          <t>-1,32; 6,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,69</t>
+          <t>-7,43; 1,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 2,63</t>
+          <t>-5,31; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,62</t>
+          <t>-1,78; 4,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 123,84</t>
+          <t>-18,12; 142,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 24,19</t>
+          <t>-55,87; 22,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 42,26</t>
+          <t>-53,35; 39,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 110,71</t>
+          <t>-24,18; 97,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,21</t>
+          <t>-3,2; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,78</t>
+          <t>-2,19; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 5,28</t>
+          <t>-2,66; 5,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,6</t>
+          <t>-5,36; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 84,93</t>
+          <t>-36,82; 108,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 140,3</t>
+          <t>-22,83; 132,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 95,33</t>
+          <t>-27,47; 93,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 26,06</t>
+          <t>-50,83; 26,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 8,37</t>
+          <t>-2,1; 9,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,27</t>
+          <t>-5,18; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 7,49</t>
+          <t>-3,69; 6,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 11,17</t>
+          <t>0,06; 12,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 129,31</t>
+          <t>-25,53; 150,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 45,74</t>
+          <t>-52,35; 41,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 101,61</t>
+          <t>-38,8; 95,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 378,67</t>
+          <t>-2,22; 436,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,47</t>
+          <t>-2,29; 2,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,53</t>
+          <t>-2,61; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,13</t>
+          <t>-2,56; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,55</t>
+          <t>-5,87; 0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 40,94</t>
+          <t>-30,38; 39,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 41,32</t>
+          <t>-22,86; 36,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 30,91</t>
+          <t>-29,07; 34,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 8,61</t>
+          <t>-65,0; 5,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,49</t>
+          <t>-4,94; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,06</t>
+          <t>-4,91; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,17</t>
+          <t>-1,62; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,09</t>
+          <t>-1,6; 5,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 29,86</t>
+          <t>-53,17; 28,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 17,95</t>
+          <t>-44,38; 18,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 78,12</t>
+          <t>-20,52; 78,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 106,97</t>
+          <t>-18,83; 106,59</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,94</t>
+          <t>-3,9; 2,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,36</t>
+          <t>-6,94; 1,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,76</t>
+          <t>-1,07; 5,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,08</t>
+          <t>1,06; 7,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 56,5</t>
+          <t>-46,88; 55,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 20,05</t>
+          <t>-49,73; 22,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 137,33</t>
+          <t>-11,07; 126,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1255,46</t>
+          <t>-13,19; 1028,15</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,75</t>
+          <t>-1,72; 0,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,28</t>
+          <t>-2,56; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,07</t>
+          <t>-0,75; 1,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,23</t>
+          <t>-1,18; 2,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 12,39</t>
+          <t>-22,83; 12,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 3,38</t>
+          <t>-24,87; 3,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 29,49</t>
+          <t>-9,13; 27,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 42,81</t>
+          <t>-16,72; 42,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 6,78</t>
+          <t>-1,3; 6,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 1,86</t>
+          <t>-7,55; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,59</t>
+          <t>-5,53; 2,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,31</t>
+          <t>-1,5; 4,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 142,78</t>
+          <t>-20,09; 128,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 22,32</t>
+          <t>-55,25; 24,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 39,96</t>
+          <t>-53,37; 39,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 97,87</t>
+          <t>-20,32; 108,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-19,81%</t>
+          <t>-24,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,02</t>
+          <t>-2,68; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,38</t>
+          <t>-2,24; 6,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,36</t>
+          <t>-2,8; 5,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,68</t>
+          <t>-5,45; 1,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 108,41</t>
+          <t>-33,36; 99,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 132,1</t>
+          <t>-25,98; 134,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 93,46</t>
+          <t>-30,51; 99,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 26,46</t>
+          <t>-51,13; 16,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,62</t>
+          <t>-2,08; 8,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,24</t>
+          <t>-5,05; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 6,42</t>
+          <t>-3,98; 7,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 12,51</t>
+          <t>-2,49; 6,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 150,47</t>
+          <t>-25,87; 133,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,35; 41,21</t>
+          <t>-49,9; 47,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 95,73</t>
+          <t>-43,94; 98,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 436,07</t>
+          <t>-23,56; 94,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-29,09%</t>
+          <t>-17,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,45</t>
+          <t>-2,28; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,32</t>
+          <t>-2,43; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,4</t>
+          <t>-2,65; 2,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,41</t>
+          <t>-3,5; 1,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 39,8</t>
+          <t>-29,3; 38,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 36,78</t>
+          <t>-22,75; 37,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 34,64</t>
+          <t>-29,97; 34,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,0; 5,48</t>
+          <t>-39,26; 15,36</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,61</t>
+          <t>-4,71; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,21</t>
+          <t>-4,99; 0,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,98</t>
+          <t>-1,54; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,0</t>
+          <t>0,47; 6,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 28,67</t>
+          <t>-53,8; 34,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 18,14</t>
+          <t>-45,73; 12,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 78,61</t>
+          <t>-20,08; 78,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 106,59</t>
+          <t>5,25; 139,05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>3,7</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>250,12%</t>
+          <t>124,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,04</t>
+          <t>-3,85; 1,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,5</t>
+          <t>-6,66; 1,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,69</t>
+          <t>-1,45; 5,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,1</t>
+          <t>-1,21; 6,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 55,09</t>
+          <t>-45,83; 54,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 22,57</t>
+          <t>-50,73; 16,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 126,06</t>
+          <t>-17,95; 130,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 1028,15</t>
+          <t>-23,51; 785,6</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,8</t>
+          <t>-1,77; 0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,28</t>
+          <t>-2,51; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,99</t>
+          <t>-0,67; 2,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,31</t>
+          <t>-0,71; 1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 12,66</t>
+          <t>-23,07; 9,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 3,76</t>
+          <t>-24,56; 4,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 27,31</t>
+          <t>-7,6; 28,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 42,81</t>
+          <t>-9,26; 27,6</t>
         </is>
       </c>
     </row>
